--- a/data/trans_orig/IP11B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP11B-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>26531</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5744,12 +5744,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>24720</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>34991</t>
+          <t>34996</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>46449</t>
+          <t>45340</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>58984</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -5842,12 +5842,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -8348,12 +8348,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -9143,12 +9143,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>29526</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -9938,12 +9938,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22191</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10023,12 +10023,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11307,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11485,12 +11485,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -11528,12 +11528,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>42088</t>
+          <t>42055</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>39775</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>53205</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>75748</t>
+          <t>75599</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>92889</t>
+          <t>92500</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -11641,12 +11641,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11711,12 +11711,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -11754,12 +11754,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -12519,7 +12519,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12868,12 +12868,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -13505,7 +13505,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -14182,12 +14182,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14217,12 +14217,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -14413,7 +14413,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -14864,12 +14864,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14899,12 +14899,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -14942,12 +14942,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14977,12 +14977,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -15012,12 +15012,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15125,12 +15125,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15238,12 +15238,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -15807,12 +15807,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15920,12 +15920,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>464</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>556</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -17249,12 +17249,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -17327,12 +17327,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17342,12 +17342,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17362,12 +17362,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>33634</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>46640</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -17440,12 +17440,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -17455,12 +17455,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -17475,12 +17475,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -17490,12 +17490,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -17510,12 +17510,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -17525,12 +17525,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -17553,12 +17553,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -17568,12 +17568,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -17588,12 +17588,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -17623,12 +17623,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -17638,12 +17638,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -18426,12 +18426,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -18441,12 +18441,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -18539,12 +18539,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -18554,12 +18554,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -19186,12 +19186,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -19201,12 +19201,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -19221,12 +19221,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -19236,12 +19236,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20633,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -20756,7 +20756,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -20776,12 +20776,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -20791,12 +20791,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -20811,12 +20811,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -20889,12 +20889,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>468</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -20904,12 +20904,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -20924,12 +20924,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -20939,12 +20939,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -21385,7 +21385,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21498,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>270</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -21551,7 +21551,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -21606,12 +21606,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>475</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -21621,12 +21621,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -21739,7 +21739,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -22900,12 +22900,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -22915,12 +22915,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -22955,7 +22955,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -22970,12 +22970,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -22985,12 +22985,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -23048,12 +23048,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -23063,12 +23063,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -23083,12 +23083,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -23098,12 +23098,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -23126,12 +23126,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -23141,12 +23141,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -23161,12 +23161,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -23176,12 +23176,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -23196,12 +23196,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -23211,12 +23211,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -23239,12 +23239,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -23254,12 +23254,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -23289,12 +23289,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -23309,12 +23309,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -23324,12 +23324,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
